--- a/data/trans_orig/IP07A15-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07A15-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que los padres tubiesen suficiente tiempo par él/ella en 2007 (tasa de respuesta: 98,9%)</t>
+          <t>Menores según la frecuencia de que los padres tuviesen suficiente tiempo par él/ella, percibida por el adulto en 2007 (tasa de respuesta: 98,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,47 +732,47 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>2803</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9459</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>25,53%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>12,45%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>42,02%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>5983</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>2866</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9336</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>25,53%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,73%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>41,47%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5983</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2976</t>
-        </is>
-      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10358</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7679</t>
+          <t>7185</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17136</t>
+          <t>17322</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>33,02%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6570</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13989</t>
+          <t>13781</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10454</t>
+          <t>10592</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19715</t>
+          <t>19383</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18927</t>
+          <t>19097</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30371</t>
+          <t>30266</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>57,7%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9600</t>
+          <t>9578</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4122</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11961</t>
+          <t>11720</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8934</t>
+          <t>9078</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19162</t>
+          <t>19289</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,77%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4494</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>678</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>5769</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26088</t>
+          <t>26940</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35476</t>
+          <t>35909</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35442</t>
+          <t>35794</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46311</t>
+          <t>46775</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65174</t>
+          <t>64685</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79491</t>
+          <t>79632</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,48%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7632</t>
+          <t>7570</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16920</t>
+          <t>16180</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9107</t>
+          <t>8575</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19835</t>
+          <t>19447</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19256</t>
+          <t>19224</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32699</t>
+          <t>33627</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>33,14%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>4435</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>548</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4982</t>
+          <t>4965</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6953</t>
+          <t>6358</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13358</t>
+          <t>13332</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23141</t>
+          <t>22483</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10625</t>
+          <t>10504</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19003</t>
+          <t>19133</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26442</t>
+          <t>25704</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39107</t>
+          <t>39320</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>60,1%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>10577</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19597</t>
+          <t>19827</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9746</t>
+          <t>9329</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17709</t>
+          <t>17930</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22185</t>
+          <t>21914</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>35634</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>54,46%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>673</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5822</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>7553</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2550</t>
+          <t>3161</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9657</t>
+          <t>9255</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19001</t>
+          <t>19122</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>9689</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20141</t>
+          <t>19764</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22215</t>
+          <t>21584</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35615</t>
+          <t>35841</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>46,13%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16499</t>
+          <t>16427</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26530</t>
+          <t>26733</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15794</t>
+          <t>16181</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>26164</t>
+          <t>26202</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>35775</t>
+          <t>35967</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>50132</t>
+          <t>50360</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,82%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>608</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>6404</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2153</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9675</t>
+          <t>9723</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3498</t>
+          <t>3933</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3079</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8180</t>
+          <t>8183</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15176</t>
+          <t>15195</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t>9063</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16894</t>
+          <t>16877</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>20155</t>
+          <t>20197</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>30720</t>
+          <t>30522</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,0%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>3796</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10877</t>
+          <t>10189</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11783</t>
+          <t>11111</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>8715</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>19289</t>
+          <t>18703</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>44,12%</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4441</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>684</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5582</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>925</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>6852</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>10342</t>
+          <t>10339</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18659</t>
+          <t>18632</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9468</t>
+          <t>9482</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>17898</t>
+          <t>17924</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,47 +4192,47 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
+          <t>60,02%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>27731</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>21918</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>33950</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>48,96%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>38,7%</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
           <t>59,94%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>27731</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>21743</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>33844</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>48,96%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>38,39%</t>
-        </is>
-      </c>
-      <c r="W34" s="2" t="inlineStr">
-        <is>
-          <t>59,75%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5848</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13832</t>
+          <t>13916</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7679</t>
+          <t>7446</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>15897</t>
+          <t>15697</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>15783</t>
+          <t>15358</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>27124</t>
+          <t>27152</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,94%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>705</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6258</t>
+          <t>6183</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2435</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>8773</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4284</t>
+          <t>4349</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>12584</t>
+          <t>12408</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>21,91%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>24557</t>
+          <t>24969</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>36990</t>
+          <t>36997</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>19259</t>
+          <t>20444</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>32096</t>
+          <t>32657</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>47947</t>
+          <t>48066</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>65307</t>
+          <t>65900</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,66%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>14560</t>
+          <t>13683</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>26473</t>
+          <t>25288</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>20571</t>
+          <t>19969</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>33532</t>
+          <t>32269</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>37463</t>
+          <t>37516</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>54442</t>
+          <t>54612</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>46,12%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>11271</t>
+          <t>11219</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>14642</t>
+          <t>15091</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>10937</t>
+          <t>10284</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>22210</t>
+          <t>22770</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,23%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>25269</t>
+          <t>25099</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>38508</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>27848</t>
+          <t>27691</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>41111</t>
+          <t>41267</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>56192</t>
+          <t>56410</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>74465</t>
+          <t>75211</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>51,08%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>26862</t>
+          <t>26296</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>41040</t>
+          <t>40015</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>24530</t>
+          <t>24693</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>38445</t>
+          <t>38288</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>55498</t>
+          <t>55600</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>74023</t>
+          <t>73519</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>49,93%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>14542</t>
+          <t>14441</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>11478</t>
+          <t>10667</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>10267</t>
+          <t>9912</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>21514</t>
+          <t>21338</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2613</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4613</t>
+          <t>4058</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>145050</t>
+          <t>143320</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>173446</t>
+          <t>172100</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>149774</t>
+          <t>149671</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>178783</t>
+          <t>177654</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>303180</t>
+          <t>298946</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>343844</t>
+          <t>341740</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>51,64%</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>113783</t>
+          <t>114229</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>141400</t>
+          <t>142264</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>123378</t>
+          <t>123813</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>154051</t>
+          <t>153391</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>245882</t>
+          <t>247523</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>286418</t>
+          <t>288973</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>23018</t>
+          <t>22370</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>40202</t>
+          <t>39451</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>28287</t>
+          <t>27856</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>47558</t>
+          <t>47264</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>54807</t>
+          <t>54271</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>81958</t>
+          <t>78720</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>633</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>5281</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>677</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>5826</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>8975</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que los padres tubiesen suficiente tiempo par él/ella en 2012 (tasa de respuesta: 97,71%)</t>
+          <t>Menores según la frecuencia de que los padres tuviesen suficiente tiempo par él/ella, percibida por el adulto en 2012 (tasa de respuesta: 97,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7106,12 +7106,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>10247</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18100</t>
+          <t>18164</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17084</t>
+          <t>17260</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25337</t>
+          <t>25151</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30228</t>
+          <t>30150</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41157</t>
+          <t>41261</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,34%</t>
         </is>
       </c>
     </row>
@@ -7219,12 +7219,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10324</t>
+          <t>10239</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9894</t>
+          <t>9783</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7289,12 +7289,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7535</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17236</t>
+          <t>16886</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7625</t>
+          <t>7496</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>4439</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2365</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -7480,47 +7480,47 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5942</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>6,91%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>19,33%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>2125</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>572</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6289</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,91%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>20,46%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2125</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>569</t>
-        </is>
-      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>6155</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -7788,12 +7788,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33343</t>
+          <t>33284</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42376</t>
+          <t>42672</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32998</t>
+          <t>33701</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44111</t>
+          <t>44268</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70323</t>
+          <t>70628</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83785</t>
+          <t>84246</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,54%</t>
         </is>
       </c>
     </row>
@@ -7901,12 +7901,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4029</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12993</t>
+          <t>12906</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6229</t>
+          <t>6163</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15657</t>
+          <t>15148</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12479</t>
+          <t>12179</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>24751</t>
+          <t>24703</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10709</t>
+          <t>10274</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -8470,12 +8470,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10634</t>
+          <t>10393</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18787</t>
+          <t>19031</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11457</t>
+          <t>11759</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21209</t>
+          <t>21589</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25593</t>
+          <t>25005</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38150</t>
+          <t>37021</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>64,62%</t>
         </is>
       </c>
     </row>
@@ -8583,12 +8583,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>5679</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13433</t>
+          <t>13646</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9320</t>
+          <t>9026</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18555</t>
+          <t>18732</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16979</t>
+          <t>17357</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28654</t>
+          <t>29464</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>51,43%</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5459</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>980</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7734</t>
+          <t>7453</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -9152,12 +9152,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9229</t>
+          <t>9048</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18961</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>9601</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19115</t>
+          <t>19292</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20320</t>
+          <t>21393</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35003</t>
+          <t>35299</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>48,37%</t>
         </is>
       </c>
     </row>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10090</t>
+          <t>10114</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19870</t>
+          <t>20269</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9280,12 +9280,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8962</t>
+          <t>8977</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18518</t>
+          <t>18605</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>21784</t>
+          <t>21282</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>35353</t>
+          <t>35617</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,81%</t>
         </is>
       </c>
     </row>
@@ -9378,12 +9378,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15095</t>
+          <t>15045</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9393,12 +9393,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9413,12 +9413,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10796</t>
+          <t>10195</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11055</t>
+          <t>11133</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23286</t>
+          <t>23095</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,65%</t>
         </is>
       </c>
     </row>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3866</t>
+          <t>3169</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4181</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9834,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8209</t>
+          <t>8804</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>16164</t>
+          <t>16350</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12839</t>
+          <t>12942</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19312</t>
+          <t>19345</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>24212</t>
+          <t>23704</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>34195</t>
+          <t>33947</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>81,97%</t>
         </is>
       </c>
     </row>
@@ -9947,12 +9947,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2339</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9374</t>
+          <t>8820</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>7862</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5697</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>14908</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,0%</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>4567</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10135,7 +10135,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -10178,7 +10178,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4507</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4736</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -10516,12 +10516,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14525</t>
+          <t>13996</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>23176</t>
+          <t>22878</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8905</t>
+          <t>8355</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>16988</t>
+          <t>16942</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>25303</t>
+          <t>25694</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>37455</t>
+          <t>38027</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>68,75%</t>
         </is>
       </c>
     </row>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>4284</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>12138</t>
+          <t>12185</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10664,12 +10664,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>13819</t>
+          <t>13636</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>11818</t>
+          <t>11442</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>23464</t>
+          <t>22991</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>41,57%</t>
         </is>
       </c>
     </row>
@@ -10742,12 +10742,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>776</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7414</t>
+          <t>6840</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10757,12 +10757,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10777,12 +10777,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>779</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7137</t>
+          <t>6758</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10792,12 +10792,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2902</t>
+          <t>2720</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>11367</t>
+          <t>11351</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>22196</t>
+          <t>22745</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>35356</t>
+          <t>35316</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11213,12 +11213,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11233,12 +11233,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>26395</t>
+          <t>26207</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>38277</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11268,12 +11268,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>54223</t>
+          <t>53423</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>71438</t>
+          <t>71191</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,11%</t>
         </is>
       </c>
     </row>
@@ -11311,12 +11311,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>15756</t>
+          <t>15623</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>28065</t>
+          <t>27483</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11326,12 +11326,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>14326</t>
+          <t>14415</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>26033</t>
+          <t>26228</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11381,12 +11381,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>33085</t>
+          <t>33416</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>50103</t>
+          <t>49847</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11396,12 +11396,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,89%</t>
         </is>
       </c>
     </row>
@@ -11424,12 +11424,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2233</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>9793</t>
+          <t>10275</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11439,12 +11439,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>612</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11474,12 +11474,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>12739</t>
+          <t>11801</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>25932</t>
+          <t>26067</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>39444</t>
+          <t>40034</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11895,12 +11895,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11915,12 +11915,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>17043</t>
+          <t>16747</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>29978</t>
+          <t>30406</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11930,12 +11930,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>46950</t>
+          <t>46295</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>66389</t>
+          <t>67022</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,46%</t>
         </is>
       </c>
     </row>
@@ -11993,12 +11993,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>31395</t>
+          <t>31155</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>45660</t>
+          <t>45788</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>36981</t>
+          <t>36779</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>51030</t>
+          <t>51503</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>72722</t>
+          <t>72987</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>93314</t>
+          <t>93485</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12078,12 +12078,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>59,22%</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3513</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>12752</t>
+          <t>12287</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>6422</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>16210</t>
+          <t>16181</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>11933</t>
+          <t>12206</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>24313</t>
+          <t>24917</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12259,7 +12259,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12294,7 +12294,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>4411</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12309,7 +12309,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>160192</t>
+          <t>158662</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>190536</t>
+          <t>189005</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>161342</t>
+          <t>161523</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>190949</t>
+          <t>190825</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12612,12 +12612,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>333256</t>
+          <t>332480</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>373581</t>
+          <t>373666</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12647,12 +12647,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>57,35%</t>
         </is>
       </c>
     </row>
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>95769</t>
+          <t>97487</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>124692</t>
+          <t>124981</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>107400</t>
+          <t>108297</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>137014</t>
+          <t>137129</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>212155</t>
+          <t>212380</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>252264</t>
+          <t>251701</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,63%</t>
         </is>
       </c>
     </row>
@@ -12788,12 +12788,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>25049</t>
+          <t>24994</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>44483</t>
+          <t>42902</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>21348</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>38177</t>
+          <t>37770</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>50336</t>
+          <t>50029</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>74767</t>
+          <t>75043</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -12901,12 +12901,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>611</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>934</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12951,12 +12951,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>2219</t>
+          <t>2155</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>10789</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3555</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13069,7 +13069,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13089,7 +13089,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13285,7 +13285,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que los padres tubiesen suficiente tiempo par él/ella en 2016 (tasa de respuesta: 98,43%)</t>
+          <t>Menores según la frecuencia de que los padres tuviesen suficiente tiempo par él/ella, percibida por el adulto en 2016 (tasa de respuesta: 98,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14501</t>
+          <t>14383</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22999</t>
+          <t>23166</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13495,12 +13495,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13515,12 +13515,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>7807</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17085</t>
+          <t>16460</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13530,12 +13530,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25057</t>
+          <t>25533</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37670</t>
+          <t>37906</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13565,12 +13565,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,54%</t>
         </is>
       </c>
     </row>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2457</t>
+          <t>2734</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8768</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13608,12 +13608,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>8225</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17041</t>
+          <t>17007</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12295</t>
+          <t>12046</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23819</t>
+          <t>23670</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>40,93%</t>
         </is>
       </c>
     </row>
@@ -13706,12 +13706,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8803</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13721,12 +13721,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13741,12 +13741,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7626</t>
+          <t>7683</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13756,12 +13756,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13026</t>
+          <t>13049</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,56%</t>
         </is>
       </c>
     </row>
@@ -13824,7 +13824,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2591</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13839,7 +13839,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2718</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13909,7 +13909,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -14162,12 +14162,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26680</t>
+          <t>27566</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39020</t>
+          <t>38767</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14177,12 +14177,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14197,12 +14197,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29931</t>
+          <t>29838</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42933</t>
+          <t>41435</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14232,12 +14232,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60327</t>
+          <t>59708</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77716</t>
+          <t>77250</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14247,12 +14247,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,17%</t>
         </is>
       </c>
     </row>
@@ -14275,12 +14275,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12008</t>
+          <t>12780</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23724</t>
+          <t>23737</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14290,12 +14290,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11527</t>
+          <t>11877</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23722</t>
+          <t>23036</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14345,12 +14345,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26655</t>
+          <t>27374</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43362</t>
+          <t>44027</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14360,12 +14360,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,99%</t>
         </is>
       </c>
     </row>
@@ -14388,12 +14388,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>652</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5656</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14403,12 +14403,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14423,12 +14423,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>8212</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14438,12 +14438,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2745</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10513</t>
+          <t>10963</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14473,12 +14473,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13555</t>
+          <t>13881</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23991</t>
+          <t>24977</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14859,12 +14859,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14879,12 +14879,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12982</t>
+          <t>13058</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22211</t>
+          <t>22597</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14894,12 +14894,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14914,12 +14914,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29069</t>
+          <t>29798</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43840</t>
+          <t>44501</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14929,12 +14929,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>63,97%</t>
         </is>
       </c>
     </row>
@@ -14957,12 +14957,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10421</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20673</t>
+          <t>20377</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14972,12 +14972,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14992,12 +14992,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8694</t>
+          <t>8775</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17709</t>
+          <t>18345</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15027,12 +15027,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21572</t>
+          <t>21426</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35997</t>
+          <t>35501</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15042,12 +15042,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,03%</t>
         </is>
       </c>
     </row>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4612</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15105,12 +15105,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>736</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6281</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15125,7 +15125,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15140,12 +15140,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8239</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15155,12 +15155,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -15188,7 +15188,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4036</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15258,7 +15258,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15273,7 +15273,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -15526,12 +15526,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25624</t>
+          <t>25157</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34787</t>
+          <t>34558</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15541,12 +15541,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15561,12 +15561,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34591</t>
+          <t>34511</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>41629</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15576,12 +15576,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15596,12 +15596,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63077</t>
+          <t>63102</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>74405</t>
+          <t>74307</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15611,12 +15611,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,14%</t>
         </is>
       </c>
     </row>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>2284</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9589</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15654,12 +15654,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15674,12 +15674,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>738</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6585</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15689,12 +15689,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15709,12 +15709,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3679</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>12676</t>
+          <t>13515</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15724,12 +15724,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -15752,12 +15752,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>618</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7546</t>
+          <t>8269</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15767,12 +15767,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15822,12 +15822,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9216</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15885,7 +15885,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15905,7 +15905,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15940,7 +15940,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -16208,12 +16208,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>4982</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12613</t>
+          <t>12433</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16223,12 +16223,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16243,12 +16243,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11651</t>
+          <t>11335</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16258,12 +16258,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16278,12 +16278,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11333</t>
+          <t>11204</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>22429</t>
+          <t>22392</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16293,12 +16293,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,36%</t>
         </is>
       </c>
     </row>
@@ -16321,12 +16321,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13112</t>
+          <t>12946</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16336,12 +16336,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12123</t>
+          <t>11805</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20143</t>
+          <t>19836</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16391,12 +16391,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>18959</t>
+          <t>19088</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>30228</t>
+          <t>30362</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16406,12 +16406,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,92%</t>
         </is>
       </c>
     </row>
@@ -16439,7 +16439,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6071</t>
+          <t>6539</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16469,12 +16469,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>621</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>5677</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16484,12 +16484,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1508</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8263</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16519,12 +16519,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,46%</t>
         </is>
       </c>
     </row>
@@ -16890,12 +16890,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>17833</t>
+          <t>18027</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>26306</t>
+          <t>26362</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16905,12 +16905,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16925,12 +16925,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>20840</t>
+          <t>20780</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>28125</t>
+          <t>28143</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16940,12 +16940,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>41729</t>
+          <t>41476</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>52516</t>
+          <t>52452</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16975,12 +16975,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,42%</t>
         </is>
       </c>
     </row>
@@ -17003,12 +17003,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2158</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9208</t>
+          <t>9312</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17018,12 +17018,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17038,12 +17038,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2342</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>9483</t>
+          <t>8881</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17053,12 +17053,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>5379</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>15224</t>
+          <t>15864</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17088,12 +17088,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -17116,12 +17116,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>980</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7711</t>
+          <t>7125</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17131,12 +17131,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8285</t>
+          <t>9288</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17201,12 +17201,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -17572,12 +17572,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>21435</t>
+          <t>20932</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>34197</t>
+          <t>34233</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -17587,12 +17587,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -17607,12 +17607,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>19340</t>
+          <t>19812</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>32981</t>
+          <t>33020</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -17622,12 +17622,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>45048</t>
+          <t>44466</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>64024</t>
+          <t>63815</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -17657,12 +17657,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,73%</t>
         </is>
       </c>
     </row>
@@ -17685,12 +17685,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>23005</t>
+          <t>22948</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>36214</t>
+          <t>36856</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -17700,12 +17700,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -17720,12 +17720,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>23362</t>
+          <t>23564</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>37269</t>
+          <t>36942</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -17735,12 +17735,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -17755,12 +17755,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>50255</t>
+          <t>50818</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>69537</t>
+          <t>69680</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -17770,12 +17770,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>53,21%</t>
         </is>
       </c>
     </row>
@@ -17798,12 +17798,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>11998</t>
+          <t>11810</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -17813,12 +17813,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -17833,12 +17833,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>10533</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -17853,7 +17853,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -17868,12 +17868,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>6876</t>
+          <t>7044</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>18781</t>
+          <t>18128</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17883,12 +17883,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -17911,12 +17911,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>713</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>6863</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -17926,12 +17926,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -17946,12 +17946,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>708</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>6692</t>
+          <t>6551</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -17981,12 +17981,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>10601</t>
+          <t>10449</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -18254,12 +18254,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>24481</t>
+          <t>24185</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>37887</t>
+          <t>37837</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -18269,12 +18269,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -18289,12 +18289,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>25736</t>
+          <t>24864</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>39502</t>
+          <t>39374</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -18304,12 +18304,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -18324,12 +18324,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>53421</t>
+          <t>52293</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>73098</t>
+          <t>71772</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -18339,12 +18339,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>45,93%</t>
         </is>
       </c>
     </row>
@@ -18367,12 +18367,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>33519</t>
+          <t>34120</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>47834</t>
+          <t>47870</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -18382,12 +18382,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -18402,12 +18402,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>29546</t>
+          <t>29452</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>43912</t>
+          <t>43656</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -18417,12 +18417,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -18437,12 +18437,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>67653</t>
+          <t>67982</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>87685</t>
+          <t>88805</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>56,83%</t>
         </is>
       </c>
     </row>
@@ -18480,12 +18480,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>14040</t>
+          <t>13318</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -18495,12 +18495,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -18515,12 +18515,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>3464</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>11703</t>
+          <t>12334</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18530,12 +18530,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18550,12 +18550,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>9241</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>21609</t>
+          <t>21620</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18565,7 +18565,7 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -18633,7 +18633,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3380</t>
+          <t>2726</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -18648,7 +18648,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -18668,7 +18668,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -18683,7 +18683,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -18936,12 +18936,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>177106</t>
+          <t>175656</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>207296</t>
+          <t>207277</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18951,12 +18951,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18971,12 +18971,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>180144</t>
+          <t>179935</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>210791</t>
+          <t>209968</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18986,12 +18986,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19006,12 +19006,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>365682</t>
+          <t>364597</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>408658</t>
+          <t>408245</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19021,12 +19021,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,18%</t>
         </is>
       </c>
     </row>
@@ -19049,12 +19049,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>114167</t>
+          <t>112328</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>143451</t>
+          <t>143418</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>118516</t>
+          <t>119256</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>148567</t>
+          <t>149030</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19099,12 +19099,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>241959</t>
+          <t>240870</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>282592</t>
+          <t>283003</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,64%</t>
         </is>
       </c>
     </row>
@@ -19162,12 +19162,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>22740</t>
+          <t>22816</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>41149</t>
+          <t>40988</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19177,12 +19177,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>17995</t>
+          <t>18012</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>35405</t>
+          <t>34353</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19217,7 +19217,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19232,12 +19232,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>44993</t>
+          <t>45085</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>68704</t>
+          <t>68805</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>9731</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19290,12 +19290,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19310,12 +19310,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>8806</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19325,12 +19325,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -19345,12 +19345,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>15020</t>
+          <t>14464</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19360,12 +19360,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
